--- a/GameConfig/Datas/文本配置表.xlsx
+++ b/GameConfig/Datas/文本配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D9328E-C0E0-4747-A54B-A6DA674BBEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44E579B-3C43-4F0F-8FDF-98225B8B6D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -120,6 +120,30 @@
   <si>
     <t>内容是 string 数组类型，数组索引对应 LocalizationType 枚举</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111{0}</t>
+  </si>
+  <si>
+    <t>11{0}11{1}</t>
+  </si>
+  <si>
+    <t>退出游戏</t>
+  </si>
+  <si>
+    <t>测试输出</t>
+  </si>
+  <si>
+    <t>测试</t>
+  </si>
+  <si>
+    <t>开始游戏</t>
+  </si>
+  <si>
+    <t>测试2</t>
+  </si>
+  <si>
+    <t>测试3</t>
   </si>
 </sst>
 </file>
@@ -268,7 +292,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,12 +352,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -613,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -679,22 +697,28 @@
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+    <row r="2" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="19"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
       <c r="N2" s="5"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -720,17 +744,11 @@
     </row>
     <row r="3" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>21</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="19"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -763,22 +781,30 @@
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
     </row>
-    <row r="4" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
       <c r="N4" s="5"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -806,19 +832,15 @@
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="10" t="s">
-        <v>16</v>
-      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="10"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -849,120 +871,121 @@
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
     </row>
-    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
+        <v>10000001</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="M6" s="8"/>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
-        <v>10000001</v>
+        <v>10000002</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J7" s="8"/>
       <c r="M7" s="8"/>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
-        <v>10000002</v>
+        <v>10000003</v>
       </c>
       <c r="C8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J8" s="8"/>
       <c r="M8" s="8"/>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
-        <v>10000003</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>20</v>
+        <v>20000001</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1111</v>
       </c>
       <c r="J9" s="8"/>
       <c r="M9" s="8"/>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="D10" s="7"/>
+      <c r="B10" s="3">
+        <v>20000002</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="J10" s="8"/>
       <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="D11" s="11"/>
+      <c r="B11" s="3">
+        <v>20000003</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
       <c r="J11" s="8"/>
       <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="B12" s="3">
+        <v>30000008</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="J12" s="8"/>
       <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="D13" s="7"/>
-      <c r="J13" s="8"/>
+      <c r="B13" s="3">
+        <v>30000009</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="J13" s="9"/>
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <v>30000010</v>
+      </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
@@ -970,30 +993,145 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <v>30000011</v>
+      </c>
       <c r="C15" s="8"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="J15" s="9"/>
+      <c r="J15" s="8"/>
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="C16" s="8"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="B16" s="3">
+        <v>30000012</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <v>30000013</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
+        <v>30000014</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <v>30000015</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <v>30000016</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>30000017</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
+        <v>30000018</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <v>30000019</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <v>30000020</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>30000021</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="3">
+        <v>30000022</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>30000023</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
+        <v>30000024</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>30000025</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="3">
+        <v>30000026</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
